--- a/Documentos Base/Sprint 8 documentacion/Sprint_08_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 8 documentacion/Sprint_08_Backlog_ICARO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 8 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF10D980-BAAA-477E-91C7-18B7AEDDFCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE112620-7A2C-4761-BECF-4853B974017E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
@@ -1347,137 +1347,105 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -1542,6 +1510,38 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1556,13 +1556,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{928470BE-63C4-4254-9D2F-E31683EE7EFC}" name="Tabla3" displayName="Tabla3" ref="A2:D15" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{928470BE-63C4-4254-9D2F-E31683EE7EFC}" name="Tabla3" displayName="Tabla3" ref="A2:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D15" xr:uid="{928470BE-63C4-4254-9D2F-E31683EE7EFC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DD3D8E04-A15E-45F9-A719-A2D69B4432EB}" name="Métrica" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{634CEE06-8BFA-46F9-9644-0C431C62D026}" name="Planificado" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{A7D2D7FC-6480-4A2E-B12F-E20068F53207}" name="Realizado" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F3418C61-C4F1-4B34-B5D9-2501EECC42FE}" name="Observación" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{DD3D8E04-A15E-45F9-A719-A2D69B4432EB}" name="Métrica" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{634CEE06-8BFA-46F9-9644-0C431C62D026}" name="Planificado" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A7D2D7FC-6480-4A2E-B12F-E20068F53207}" name="Realizado" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F3418C61-C4F1-4B34-B5D9-2501EECC42FE}" name="Observación" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1864,424 +1864,424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="16" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
     </row>
     <row r="4" spans="1:12" ht="24">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="34">
         <v>46174</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="16" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="34">
         <v>46178</v>
       </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
     </row>
     <row r="5" spans="1:12" ht="107.25" customHeight="1">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="16" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
     </row>
     <row r="6" spans="1:12" ht="24">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="16" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:12" ht="30">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="190.5">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:12" ht="147.75">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="8">
         <v>10</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>10</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="165">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:12" ht="135">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="8">
         <v>8</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>8</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="118.5" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="8">
         <v>5</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <v>5</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="10" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="142.5" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="8">
         <v>8</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <v>8</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="10" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="120">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="8">
         <v>8</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="8">
         <v>8</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="135">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:12" ht="120">
+      <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>5</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="26">
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="13">
         <v>44</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="13">
         <v>44</v>
       </c>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2300,14 +2300,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
@@ -2848,206 +2848,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="17" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="14">
         <v>44</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="14">
         <v>44</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="14" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="14">
         <v>5</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="14">
         <v>5</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="14" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="14">
         <v>1</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="14">
         <v>6</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="14">
         <v>6</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="14" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="14">
         <v>6</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="14">
         <v>6</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="14">
         <v>0</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="14">
         <v>0</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="14" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="14">
         <v>0</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="14">
         <v>0</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="14" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="14">
         <v>44</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="14">
         <v>44</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="14" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="15">
         <v>1</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="15">
         <v>1</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="14" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="14">
         <v>25</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="14">
         <v>25</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="14" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="15">
         <v>1</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="14" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="16">
         <v>46179</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="16">
         <v>46179</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="14" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="14">
         <v>193</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="14">
         <v>193</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="14" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3072,185 +3072,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="20" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="22" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="20" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="22" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="22" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="20" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="22" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="20" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="22" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="20" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="22" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="20" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="22" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="20" t="s">
         <v>239</v>
       </c>
     </row>
